--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/CALIFORNIA_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/CALIFORNIA_2016.xlsx
@@ -4920,7 +4920,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C254">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C420">
@@ -7933,7 +7933,7 @@
         <v>216</v>
       </c>
       <c r="D421">
-        <v>0.0009152193348558741</v>
+        <v>0.000915219334855874</v>
       </c>
     </row>
     <row r="422">
@@ -8599,7 +8599,7 @@
         <v>235</v>
       </c>
       <c r="D458">
-        <v>0.0009957247393107889</v>
+        <v>0.0009957247393107887</v>
       </c>
     </row>
     <row r="459">
@@ -9715,7 +9715,7 @@
         <v>226</v>
       </c>
       <c r="D520">
-        <v>0.0009575906003584609</v>
+        <v>0.0009575906003584608</v>
       </c>
     </row>
     <row r="521">
@@ -11713,7 +11713,7 @@
         <v>236</v>
       </c>
       <c r="D631">
-        <v>0.0009999618658610477</v>
+        <v>0.0009999618658610475</v>
       </c>
     </row>
     <row r="632">
@@ -11911,7 +11911,7 @@
         <v>235</v>
       </c>
       <c r="D642">
-        <v>0.0009957247393107889</v>
+        <v>0.0009957247393107887</v>
       </c>
     </row>
     <row r="643">
@@ -13045,7 +13045,7 @@
         <v>216</v>
       </c>
       <c r="D705">
-        <v>0.0009152193348558741</v>
+        <v>0.000915219334855874</v>
       </c>
     </row>
     <row r="706">
@@ -14899,7 +14899,7 @@
         <v>226</v>
       </c>
       <c r="D808">
-        <v>0.0009575906003584609</v>
+        <v>0.0009575906003584608</v>
       </c>
     </row>
     <row r="809">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C918">
@@ -20850,7 +20850,7 @@
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 08-</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1139">
@@ -20868,7 +20868,7 @@
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 26-</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1140">
@@ -22632,7 +22632,7 @@
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1238">
@@ -22650,7 +22650,7 @@
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1239">
@@ -23215,7 +23215,7 @@
         <v>218</v>
       </c>
       <c r="D1270">
-        <v>0.0009236935879563915</v>
+        <v>0.0009236935879563916</v>
       </c>
     </row>
     <row r="1271">
@@ -26016,7 +26016,7 @@
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C1426">
@@ -30037,7 +30037,7 @@
         <v>228</v>
       </c>
       <c r="D1649">
-        <v>0.0009660648534589783</v>
+        <v>0.0009660648534589784</v>
       </c>
     </row>
     <row r="1650">
@@ -32377,7 +32377,7 @@
         <v>218</v>
       </c>
       <c r="D1779">
-        <v>0.0009236935879563915</v>
+        <v>0.0009236935879563916</v>
       </c>
     </row>
     <row r="1780">
@@ -32485,7 +32485,7 @@
         <v>226</v>
       </c>
       <c r="D1785">
-        <v>0.0009575906003584609</v>
+        <v>0.0009575906003584608</v>
       </c>
     </row>
     <row r="1786">
@@ -34735,7 +34735,7 @@
         <v>216</v>
       </c>
       <c r="D1910">
-        <v>0.0009152193348558741</v>
+        <v>0.000915219334855874</v>
       </c>
     </row>
     <row r="1911">
@@ -35610,7 +35610,7 @@
       </c>
       <c r="B1959" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1959">
@@ -41575,7 +41575,7 @@
         <v>235</v>
       </c>
       <c r="D2290">
-        <v>0.0009957247393107889</v>
+        <v>0.0009957247393107887</v>
       </c>
     </row>
     <row r="2291">
